--- a/data/trans_orig/IP1018-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1018-Clase-trans_orig.xlsx
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197423</t>
+          <t>197465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398994</t>
+          <t>399526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71564</t>
+          <t>71605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67822</t>
+          <t>68092</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142085</t>
+          <t>141084</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146738</t>
+          <t>146739</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>720</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634114</t>
+          <t>633923</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>680040</t>
+          <t>680341</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316799</t>
+          <t>1316913</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1322803</t>
+          <t>1322739</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80482</t>
+          <t>79697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179641</t>
+          <t>179707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>219729</t>
+          <t>220097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207866</t>
+          <t>207886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430221</t>
+          <t>430836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>133243</t>
+          <t>133522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137113</t>
+          <t>137091</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272818</t>
+          <t>273276</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>666523</t>
+          <t>666587</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>670922</t>
+          <t>670920</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>703842</t>
+          <t>703808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1373149</t>
+          <t>1372963</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1380064</t>
+          <t>1380052</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/IP1018-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1018-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1183,42 +1183,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200079</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>197465</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>197409</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>606</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399526</t>
+          <t>399548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1244</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3265</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1244</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4300</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>526</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -2550,74 +2550,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>71148</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>67319</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74150</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>71605</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>71302</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>99,04%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>95,23%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>71148</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>68092</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>216</t>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>141084</t>
+          <t>141717</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146739</t>
+          <t>146736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2785,67 +2785,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>1244</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4654</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>1374</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4933</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4165</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1244</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4262</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>683359</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>679949</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>637482</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>633923</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>634691</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,79%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1027</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>683359</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>680341</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1978</t>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316913</t>
+          <t>1317150</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1322739</t>
+          <t>1322741</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3470,47 +3470,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3813,47 +3813,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4156,47 +4156,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4499,47 +4499,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4842,47 +4842,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5185,47 +5185,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5528,47 +5528,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,107 +5992,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>638</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3393</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3307</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3221</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3180</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -6105,74 +6105,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>82452</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>79697</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>79783</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,23%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>270</t>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179707</t>
+          <t>179666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6448,47 +6448,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6791,47 +6791,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7026,102 +7026,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3494</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>604</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3480</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2968</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3595</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -7134,74 +7134,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210266</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>207360</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>222973</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>220097</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>220515</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210266</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>207886</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>640</t>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430836</t>
+          <t>430359</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7369,102 +7369,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>583</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2672</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3518</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1088</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5997</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1671</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6582</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1671</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>6006</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -7477,74 +7477,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>142000</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>137824</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>135611</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>133522</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>132676</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>142000</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>137091</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>402</t>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273276</t>
+          <t>272700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6217</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1824</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>582</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4915</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5455</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5929</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -8163,74 +8163,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>708061</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>703520</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1010</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>669678</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>666587</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>666047</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>670920</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,73%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>708061</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>703808</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,76%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>2025</t>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1372963</t>
+          <t>1373191</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1380052</t>
+          <t>1380019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
